--- a/pca-interpretable-clustering/classified_data/Carbide.xlsx
+++ b/pca-interpretable-clustering/classified_data/Carbide.xlsx
@@ -3156,7 +3156,7 @@
         <v>10.58035</v>
       </c>
       <c r="H2">
-        <v>114.03349</v>
+        <v>114.0334925</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -3182,7 +3182,7 @@
         <v>202.00525</v>
       </c>
       <c r="H3">
-        <v>464.6944</v>
+        <v>464.6944002</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -3208,7 +3208,7 @@
         <v>209.28553</v>
       </c>
       <c r="H4">
-        <v>473.66261</v>
+        <v>473.6626123</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -3234,7 +3234,7 @@
         <v>38.63868</v>
       </c>
       <c r="H5">
-        <v>223.22085</v>
+        <v>223.2208533</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -3260,7 +3260,7 @@
         <v>203.8825</v>
       </c>
       <c r="H6">
-        <v>428.37096</v>
+        <v>428.3709625</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -3286,7 +3286,7 @@
         <v>152.61682</v>
       </c>
       <c r="H7">
-        <v>317.02641</v>
+        <v>317.0264118</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -3312,7 +3312,7 @@
         <v>206.58011</v>
       </c>
       <c r="H8">
-        <v>429.15658</v>
+        <v>429.1565788</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -3338,7 +3338,7 @@
         <v>179.98867</v>
       </c>
       <c r="H9">
-        <v>405.08517</v>
+        <v>405.0851742</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -3364,7 +3364,7 @@
         <v>202.06296</v>
       </c>
       <c r="H10">
-        <v>429.57624</v>
+        <v>429.5762432</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -3390,7 +3390,7 @@
         <v>183.87261</v>
       </c>
       <c r="H11">
-        <v>407.00758</v>
+        <v>407.0075782</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -3416,7 +3416,7 @@
         <v>37.89122</v>
       </c>
       <c r="H12">
-        <v>330.19491</v>
+        <v>330.1949104</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -3442,7 +3442,7 @@
         <v>227.24578</v>
       </c>
       <c r="H13">
-        <v>416.26778</v>
+        <v>416.2677796</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -3468,7 +3468,7 @@
         <v>49.37967</v>
       </c>
       <c r="H14">
-        <v>418.42683</v>
+        <v>418.4268303</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -3494,7 +3494,7 @@
         <v>64.12356</v>
       </c>
       <c r="H15">
-        <v>244.75911</v>
+        <v>244.7591066</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -3520,7 +3520,7 @@
         <v>31.03405</v>
       </c>
       <c r="H16">
-        <v>228.79425</v>
+        <v>228.7942458</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -3572,7 +3572,7 @@
         <v>198.73728</v>
       </c>
       <c r="H18">
-        <v>429.90225</v>
+        <v>429.9022489</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -3598,7 +3598,7 @@
         <v>49.6477</v>
       </c>
       <c r="H19">
-        <v>294.12845</v>
+        <v>294.1284492</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -3624,7 +3624,7 @@
         <v>193.8757</v>
       </c>
       <c r="H20">
-        <v>413.146</v>
+        <v>413.1460044</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -3650,7 +3650,7 @@
         <v>210.88954</v>
       </c>
       <c r="H21">
-        <v>430.16757</v>
+        <v>430.1675706</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -3676,7 +3676,7 @@
         <v>179.47068</v>
       </c>
       <c r="H22">
-        <v>490.36007</v>
+        <v>490.3600653</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -3702,7 +3702,7 @@
         <v>200.33537</v>
       </c>
       <c r="H23">
-        <v>509.6244</v>
+        <v>509.624402</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -3728,7 +3728,7 @@
         <v>185.56542</v>
       </c>
       <c r="H24">
-        <v>374.63493</v>
+        <v>374.6349269</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -3754,7 +3754,7 @@
         <v>15.94926</v>
       </c>
       <c r="H25">
-        <v>142.02952</v>
+        <v>142.0295243</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -3780,7 +3780,7 @@
         <v>393.46445</v>
       </c>
       <c r="H26">
-        <v>658.90314</v>
+        <v>658.903137</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -3806,7 +3806,7 @@
         <v>22.62535</v>
       </c>
       <c r="H27">
-        <v>172.23027</v>
+        <v>172.2302699</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -3832,7 +3832,7 @@
         <v>32.15781</v>
       </c>
       <c r="H28">
-        <v>301.77191</v>
+        <v>301.7719112</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -3884,7 +3884,7 @@
         <v>192.395</v>
       </c>
       <c r="H30">
-        <v>410.97411</v>
+        <v>410.9741133</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -3910,7 +3910,7 @@
         <v>28.26516</v>
       </c>
       <c r="H31">
-        <v>223.84782</v>
+        <v>223.8478187</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -3936,7 +3936,7 @@
         <v>255.66324</v>
       </c>
       <c r="H32">
-        <v>720.17521</v>
+        <v>720.1752086</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -3962,7 +3962,7 @@
         <v>61.49715</v>
       </c>
       <c r="H33">
-        <v>429.85067</v>
+        <v>429.850666</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -3988,7 +3988,7 @@
         <v>71.87472</v>
       </c>
       <c r="H34">
-        <v>572.72878</v>
+        <v>572.7287807</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -4014,7 +4014,7 @@
         <v>55.36933</v>
       </c>
       <c r="H35">
-        <v>319.37335</v>
+        <v>319.3733518</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -4040,7 +4040,7 @@
         <v>552.3163</v>
       </c>
       <c r="H36">
-        <v>764.985</v>
+        <v>764.9849975</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -4066,7 +4066,7 @@
         <v>667.53866</v>
       </c>
       <c r="H37">
-        <v>1679.18093</v>
+        <v>1679.180925</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -4092,7 +4092,7 @@
         <v>249.94629</v>
       </c>
       <c r="H38">
-        <v>487.24073</v>
+        <v>487.2407344</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -4118,7 +4118,7 @@
         <v>246.95524</v>
       </c>
       <c r="H39">
-        <v>490.17139</v>
+        <v>490.1713886</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -4144,7 +4144,7 @@
         <v>194.25957</v>
       </c>
       <c r="H40">
-        <v>470.1376</v>
+        <v>470.1376019</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -4196,7 +4196,7 @@
         <v>216.82637</v>
       </c>
       <c r="H42">
-        <v>488.28827</v>
+        <v>488.2882657</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -4222,7 +4222,7 @@
         <v>212.11267</v>
       </c>
       <c r="H43">
-        <v>488.52355</v>
+        <v>488.5235493</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -4248,7 +4248,7 @@
         <v>242.31869</v>
       </c>
       <c r="H44">
-        <v>489.80748</v>
+        <v>489.8074829</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -4274,7 +4274,7 @@
         <v>236.04192</v>
       </c>
       <c r="H45">
-        <v>490.48807</v>
+        <v>490.4880683</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -4300,7 +4300,7 @@
         <v>239.54647</v>
       </c>
       <c r="H46">
-        <v>431.62046</v>
+        <v>431.6204599</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -4326,7 +4326,7 @@
         <v>251.43864</v>
       </c>
       <c r="H47">
-        <v>487.23886</v>
+        <v>487.2388625</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -4352,7 +4352,7 @@
         <v>250.8953</v>
       </c>
       <c r="H48">
-        <v>488.27093</v>
+        <v>488.270929</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -4378,7 +4378,7 @@
         <v>238.7769</v>
       </c>
       <c r="H49">
-        <v>578.23918</v>
+        <v>578.2391755</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -4404,7 +4404,7 @@
         <v>388.83407</v>
       </c>
       <c r="H50">
-        <v>587.04953</v>
+        <v>587.0495307</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -4430,7 +4430,7 @@
         <v>308.60314</v>
       </c>
       <c r="H51">
-        <v>681.99697</v>
+        <v>681.9969749000001</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -4456,7 +4456,7 @@
         <v>86.99396</v>
       </c>
       <c r="H52">
-        <v>472.53883</v>
+        <v>472.5388267</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -4482,7 +4482,7 @@
         <v>57.63382</v>
       </c>
       <c r="H53">
-        <v>305.60146</v>
+        <v>305.6014603</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -4508,7 +4508,7 @@
         <v>12.10314</v>
       </c>
       <c r="H54">
-        <v>140.11807</v>
+        <v>140.1180684</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -4534,7 +4534,7 @@
         <v>212.28838</v>
       </c>
       <c r="H55">
-        <v>586.73849</v>
+        <v>586.7384874000001</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -4560,7 +4560,7 @@
         <v>57.23679</v>
       </c>
       <c r="H56">
-        <v>255.11281</v>
+        <v>255.1128123</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -4586,7 +4586,7 @@
         <v>64.8959</v>
       </c>
       <c r="H57">
-        <v>310.05019</v>
+        <v>310.0501944</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -4612,7 +4612,7 @@
         <v>75.75072</v>
       </c>
       <c r="H58">
-        <v>396.20571</v>
+        <v>396.2057081</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -4638,7 +4638,7 @@
         <v>367.24464</v>
       </c>
       <c r="H59">
-        <v>499.72079</v>
+        <v>499.7207856</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -4664,7 +4664,7 @@
         <v>428.87806</v>
       </c>
       <c r="H60">
-        <v>798.56274</v>
+        <v>798.5627402</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -4690,7 +4690,7 @@
         <v>303.17002</v>
       </c>
       <c r="H61">
-        <v>537.73328</v>
+        <v>537.733284</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -4716,7 +4716,7 @@
         <v>185.71238</v>
       </c>
       <c r="H62">
-        <v>401.60448</v>
+        <v>401.6044814</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -4742,7 +4742,7 @@
         <v>202.19438</v>
       </c>
       <c r="H63">
-        <v>394.69169</v>
+        <v>394.6916903</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -4768,7 +4768,7 @@
         <v>256.97407</v>
       </c>
       <c r="H64">
-        <v>1020.36457</v>
+        <v>1020.364567</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -4794,7 +4794,7 @@
         <v>323.50707</v>
       </c>
       <c r="H65">
-        <v>598.8797499999999</v>
+        <v>598.8797530000001</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -4820,7 +4820,7 @@
         <v>312.84703</v>
       </c>
       <c r="H66">
-        <v>597.98696</v>
+        <v>597.9869616</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -4846,7 +4846,7 @@
         <v>318.61652</v>
       </c>
       <c r="H67">
-        <v>598.76738</v>
+        <v>598.7673777</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -4872,7 +4872,7 @@
         <v>72.55534</v>
       </c>
       <c r="H68">
-        <v>687.28062</v>
+        <v>687.2806169</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -4898,7 +4898,7 @@
         <v>304.79758</v>
       </c>
       <c r="H69">
-        <v>597.02914</v>
+        <v>597.0291353</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -4924,7 +4924,7 @@
         <v>295.95129</v>
       </c>
       <c r="H70">
-        <v>764.97943</v>
+        <v>764.9794272</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -4950,7 +4950,7 @@
         <v>296.54396</v>
       </c>
       <c r="H71">
-        <v>772.0653600000001</v>
+        <v>772.0653648</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -4976,7 +4976,7 @@
         <v>488.02442</v>
       </c>
       <c r="H72">
-        <v>1497.65431</v>
+        <v>1497.654313</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -5002,7 +5002,7 @@
         <v>447.1576</v>
       </c>
       <c r="H73">
-        <v>1443.66284</v>
+        <v>1443.662844</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -5028,7 +5028,7 @@
         <v>65.84313</v>
       </c>
       <c r="H74">
-        <v>386.94066</v>
+        <v>386.9406601</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -5054,7 +5054,7 @@
         <v>301.39958</v>
       </c>
       <c r="H75">
-        <v>699.92291</v>
+        <v>699.9229093</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -5080,7 +5080,7 @@
         <v>300.53428</v>
       </c>
       <c r="H76">
-        <v>637.00548</v>
+        <v>637.0054817</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -5106,7 +5106,7 @@
         <v>299.86737</v>
       </c>
       <c r="H77">
-        <v>646.38625</v>
+        <v>646.3862471</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -5132,7 +5132,7 @@
         <v>285.87006</v>
       </c>
       <c r="H78">
-        <v>679.9527399999999</v>
+        <v>679.9527421</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -5158,7 +5158,7 @@
         <v>291.2842</v>
       </c>
       <c r="H79">
-        <v>662.87199</v>
+        <v>662.8719853</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -5184,7 +5184,7 @@
         <v>298.17064</v>
       </c>
       <c r="H80">
-        <v>651.73226</v>
+        <v>651.7322553</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -5210,7 +5210,7 @@
         <v>301.26286</v>
       </c>
       <c r="H81">
-        <v>633.88554</v>
+        <v>633.8855366</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -5262,7 +5262,7 @@
         <v>168.15044</v>
       </c>
       <c r="H83">
-        <v>368.29303</v>
+        <v>368.2930293</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -5288,7 +5288,7 @@
         <v>154.8925</v>
       </c>
       <c r="H84">
-        <v>350.29904</v>
+        <v>350.2990435</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -5314,7 +5314,7 @@
         <v>167.90796</v>
       </c>
       <c r="H85">
-        <v>361.66157</v>
+        <v>361.6615711</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -5340,7 +5340,7 @@
         <v>153.59491</v>
       </c>
       <c r="H86">
-        <v>425.71106</v>
+        <v>425.7110638</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -5366,7 +5366,7 @@
         <v>327.55445</v>
       </c>
       <c r="H87">
-        <v>802.86252</v>
+        <v>802.8625207</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -5392,7 +5392,7 @@
         <v>186.63467</v>
       </c>
       <c r="H88">
-        <v>447.88509</v>
+        <v>447.8850871</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -5418,7 +5418,7 @@
         <v>191.66911</v>
       </c>
       <c r="H89">
-        <v>450.58491</v>
+        <v>450.5849057</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -5444,7 +5444,7 @@
         <v>103.8321</v>
       </c>
       <c r="H90">
-        <v>328.75916</v>
+        <v>328.7591566</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -5470,7 +5470,7 @@
         <v>170.7552</v>
       </c>
       <c r="H91">
-        <v>426.53469</v>
+        <v>426.5346937</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -5496,7 +5496,7 @@
         <v>160.23852</v>
       </c>
       <c r="H92">
-        <v>386.66589</v>
+        <v>386.6658855</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -5522,7 +5522,7 @@
         <v>100.39964</v>
       </c>
       <c r="H93">
-        <v>347.48545</v>
+        <v>347.4854534</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -5548,7 +5548,7 @@
         <v>181.19763</v>
       </c>
       <c r="H94">
-        <v>464.21052</v>
+        <v>464.2105249</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -5574,7 +5574,7 @@
         <v>51.49388</v>
       </c>
       <c r="H95">
-        <v>526.30759</v>
+        <v>526.3075936</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -5600,7 +5600,7 @@
         <v>99.16795999999999</v>
       </c>
       <c r="H96">
-        <v>334.43623</v>
+        <v>334.4362289</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -5626,7 +5626,7 @@
         <v>177.60628</v>
       </c>
       <c r="H97">
-        <v>451.86078</v>
+        <v>451.8607761</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -5652,7 +5652,7 @@
         <v>96.25884000000001</v>
       </c>
       <c r="H98">
-        <v>334.51493</v>
+        <v>334.5149312</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -5678,7 +5678,7 @@
         <v>176.41091</v>
       </c>
       <c r="H99">
-        <v>645.58713</v>
+        <v>645.5871332</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -5704,7 +5704,7 @@
         <v>99.89413999999999</v>
       </c>
       <c r="H100">
-        <v>326.52537</v>
+        <v>326.5253662</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -5730,7 +5730,7 @@
         <v>107.24314</v>
       </c>
       <c r="H101">
-        <v>326.62687</v>
+        <v>326.6268745</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -5756,7 +5756,7 @@
         <v>187.638</v>
       </c>
       <c r="H102">
-        <v>452.39776</v>
+        <v>452.3977616</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -5782,7 +5782,7 @@
         <v>191.08239</v>
       </c>
       <c r="H103">
-        <v>450.47516</v>
+        <v>450.4751604</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -5808,7 +5808,7 @@
         <v>137.89446</v>
       </c>
       <c r="H104">
-        <v>246.51095</v>
+        <v>246.5109544</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -5834,7 +5834,7 @@
         <v>202.40062</v>
       </c>
       <c r="H105">
-        <v>343.50555</v>
+        <v>343.5055523</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -5860,7 +5860,7 @@
         <v>244.8589</v>
       </c>
       <c r="H106">
-        <v>457.77243</v>
+        <v>457.7724307</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -5886,7 +5886,7 @@
         <v>231.45993</v>
       </c>
       <c r="H107">
-        <v>893.94934</v>
+        <v>893.9493419</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -5912,7 +5912,7 @@
         <v>107.35975</v>
       </c>
       <c r="H108">
-        <v>576.2885199999999</v>
+        <v>576.2885203</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -5938,7 +5938,7 @@
         <v>422.38728</v>
       </c>
       <c r="H109">
-        <v>857.75542</v>
+        <v>857.7554152</v>
       </c>
     </row>
     <row r="110" spans="1:8">
@@ -5964,7 +5964,7 @@
         <v>32.77394</v>
       </c>
       <c r="H110">
-        <v>355.90015</v>
+        <v>355.9001462</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -5990,7 +5990,7 @@
         <v>162.47884</v>
       </c>
       <c r="H111">
-        <v>372.17638</v>
+        <v>350.360344</v>
       </c>
     </row>
     <row r="112" spans="1:8">
@@ -6016,7 +6016,7 @@
         <v>44.17323</v>
       </c>
       <c r="H112">
-        <v>209.03017</v>
+        <v>209.030173</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -6042,7 +6042,7 @@
         <v>29.42365</v>
       </c>
       <c r="H113">
-        <v>246.8057</v>
+        <v>246.8056978</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -6068,7 +6068,7 @@
         <v>56.60755</v>
       </c>
       <c r="H114">
-        <v>212.0546</v>
+        <v>212.054599</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -6094,7 +6094,7 @@
         <v>38.10908</v>
       </c>
       <c r="H115">
-        <v>176.74001</v>
+        <v>176.7400116</v>
       </c>
     </row>
     <row r="116" spans="1:8">
@@ -6120,7 +6120,7 @@
         <v>368.26134</v>
       </c>
       <c r="H116">
-        <v>431.2527</v>
+        <v>431.2527049</v>
       </c>
     </row>
     <row r="117" spans="1:8">
@@ -6146,7 +6146,7 @@
         <v>273.74972</v>
       </c>
       <c r="H117">
-        <v>900.45746</v>
+        <v>900.4574566</v>
       </c>
     </row>
     <row r="118" spans="1:8">
@@ -6172,7 +6172,7 @@
         <v>55.34928</v>
       </c>
       <c r="H118">
-        <v>410.29179</v>
+        <v>410.2917851</v>
       </c>
     </row>
     <row r="119" spans="1:8">
@@ -6198,7 +6198,7 @@
         <v>72.59547999999999</v>
       </c>
       <c r="H119">
-        <v>337.28854</v>
+        <v>337.2885421</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -6224,7 +6224,7 @@
         <v>468.04096</v>
       </c>
       <c r="H120">
-        <v>528.03788</v>
+        <v>463.3354689</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -6250,7 +6250,7 @@
         <v>69.9529</v>
       </c>
       <c r="H121">
-        <v>213.08436</v>
+        <v>213.0843633</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -6276,7 +6276,7 @@
         <v>74.13875</v>
       </c>
       <c r="H122">
-        <v>217.15453</v>
+        <v>217.1545323</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -6302,7 +6302,7 @@
         <v>56.4745</v>
       </c>
       <c r="H123">
-        <v>403.50076</v>
+        <v>403.5007617</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -6328,7 +6328,7 @@
         <v>85.87093</v>
       </c>
       <c r="H124">
-        <v>545.95415</v>
+        <v>545.9541464</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -6354,7 +6354,7 @@
         <v>62.65975</v>
       </c>
       <c r="H125">
-        <v>203.53412</v>
+        <v>203.534115</v>
       </c>
     </row>
     <row r="126" spans="1:8">
@@ -6380,7 +6380,7 @@
         <v>303.07555</v>
       </c>
       <c r="H126">
-        <v>531.30602</v>
+        <v>531.3060228000001</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -6406,7 +6406,7 @@
         <v>245.19545</v>
       </c>
       <c r="H127">
-        <v>661.17209</v>
+        <v>661.1720894</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -6432,7 +6432,7 @@
         <v>80.85595000000001</v>
       </c>
       <c r="H128">
-        <v>307.71927</v>
+        <v>289.3805945</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -6458,7 +6458,7 @@
         <v>86.80410999999999</v>
       </c>
       <c r="H129">
-        <v>507.849</v>
+        <v>507.8490005</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -6484,7 +6484,7 @@
         <v>79.25154000000001</v>
       </c>
       <c r="H130">
-        <v>362.63517</v>
+        <v>362.635169</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -6510,7 +6510,7 @@
         <v>143.0401</v>
       </c>
       <c r="H131">
-        <v>685.26483</v>
+        <v>685.2648304000001</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -6536,7 +6536,7 @@
         <v>116.9015</v>
       </c>
       <c r="H132">
-        <v>501.64169</v>
+        <v>501.6416922</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -6562,7 +6562,7 @@
         <v>74.03834999999999</v>
       </c>
       <c r="H133">
-        <v>458.8779</v>
+        <v>458.8779012</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -6588,7 +6588,7 @@
         <v>589.13051</v>
       </c>
       <c r="H134">
-        <v>800.18849</v>
+        <v>737.219001</v>
       </c>
     </row>
     <row r="135" spans="1:8">
@@ -6614,7 +6614,7 @@
         <v>641.56214</v>
       </c>
       <c r="H135">
-        <v>620.85929</v>
+        <v>620.8592949</v>
       </c>
     </row>
     <row r="136" spans="1:8">
@@ -6640,7 +6640,7 @@
         <v>254.52948</v>
       </c>
       <c r="H136">
-        <v>1117.43724</v>
+        <v>1117.437237</v>
       </c>
     </row>
     <row r="137" spans="1:8">
@@ -6666,7 +6666,7 @@
         <v>338.31209</v>
       </c>
       <c r="H137">
-        <v>756.54023</v>
+        <v>756.5402305</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -6692,7 +6692,7 @@
         <v>320.60333</v>
       </c>
       <c r="H138">
-        <v>753.48034</v>
+        <v>753.4803379</v>
       </c>
     </row>
     <row r="139" spans="1:8">
@@ -6718,7 +6718,7 @@
         <v>90.30907999999999</v>
       </c>
       <c r="H139">
-        <v>402.38649</v>
+        <v>402.3864914</v>
       </c>
     </row>
     <row r="140" spans="1:8">
@@ -6744,7 +6744,7 @@
         <v>296.01118</v>
       </c>
       <c r="H140">
-        <v>615.85777</v>
+        <v>615.8577726</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -6770,7 +6770,7 @@
         <v>306.98904</v>
       </c>
       <c r="H141">
-        <v>450.15798</v>
+        <v>450.1579777</v>
       </c>
     </row>
     <row r="142" spans="1:8">
@@ -6796,7 +6796,7 @@
         <v>309.96974</v>
       </c>
       <c r="H142">
-        <v>1308.56343</v>
+        <v>1308.563429</v>
       </c>
     </row>
     <row r="143" spans="1:8">
@@ -6822,7 +6822,7 @@
         <v>276.74454</v>
       </c>
       <c r="H143">
-        <v>567.55574</v>
+        <v>567.5557429</v>
       </c>
     </row>
     <row r="144" spans="1:8">
@@ -6848,7 +6848,7 @@
         <v>292.65036</v>
       </c>
       <c r="H144">
-        <v>523.76994</v>
+        <v>523.7699364</v>
       </c>
     </row>
     <row r="145" spans="1:8">
@@ -6874,7 +6874,7 @@
         <v>246.54984</v>
       </c>
       <c r="H145">
-        <v>458.57771</v>
+        <v>458.5777112</v>
       </c>
     </row>
     <row r="146" spans="1:8">
@@ -6900,7 +6900,7 @@
         <v>327.74576</v>
       </c>
       <c r="H146">
-        <v>600.66079</v>
+        <v>600.6607886</v>
       </c>
     </row>
     <row r="147" spans="1:8">
@@ -6926,7 +6926,7 @@
         <v>330.16935</v>
       </c>
       <c r="H147">
-        <v>619.1898200000001</v>
+        <v>619.1898198</v>
       </c>
     </row>
     <row r="148" spans="1:8">
@@ -6952,7 +6952,7 @@
         <v>93.04268</v>
       </c>
       <c r="H148">
-        <v>274.24741</v>
+        <v>274.2474109</v>
       </c>
     </row>
     <row r="149" spans="1:8">
@@ -6978,7 +6978,7 @@
         <v>660.0445</v>
       </c>
       <c r="H149">
-        <v>559.21735</v>
+        <v>559.217347</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -7004,7 +7004,7 @@
         <v>323.4504</v>
       </c>
       <c r="H150">
-        <v>763.25987</v>
+        <v>763.2598688</v>
       </c>
     </row>
     <row r="151" spans="1:8">
@@ -7030,7 +7030,7 @@
         <v>262.13385</v>
       </c>
       <c r="H151">
-        <v>622.88496</v>
+        <v>622.8849619</v>
       </c>
     </row>
     <row r="152" spans="1:8">
@@ -7056,7 +7056,7 @@
         <v>258.78851</v>
       </c>
       <c r="H152">
-        <v>604.46684</v>
+        <v>604.4668421</v>
       </c>
     </row>
     <row r="153" spans="1:8">
@@ -7082,7 +7082,7 @@
         <v>300.4709</v>
       </c>
       <c r="H153">
-        <v>683.94591</v>
+        <v>683.9459139000001</v>
       </c>
     </row>
     <row r="154" spans="1:8">
@@ -7108,7 +7108,7 @@
         <v>290.68103</v>
       </c>
       <c r="H154">
-        <v>607.37909</v>
+        <v>607.3790944</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -7134,7 +7134,7 @@
         <v>262.1197</v>
       </c>
       <c r="H155">
-        <v>580.50173</v>
+        <v>580.5017331</v>
       </c>
     </row>
     <row r="156" spans="1:8">
@@ -7160,7 +7160,7 @@
         <v>371.73437</v>
       </c>
       <c r="H156">
-        <v>781.92218</v>
+        <v>781.9221802</v>
       </c>
     </row>
     <row r="157" spans="1:8">
@@ -7186,7 +7186,7 @@
         <v>278.49518</v>
       </c>
       <c r="H157">
-        <v>574.07059</v>
+        <v>574.0705887</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -7212,7 +7212,7 @@
         <v>206.01944</v>
       </c>
       <c r="H158">
-        <v>436.27794</v>
+        <v>436.2779436</v>
       </c>
     </row>
     <row r="159" spans="1:8">
@@ -7238,7 +7238,7 @@
         <v>194.24562</v>
       </c>
       <c r="H159">
-        <v>415.4033</v>
+        <v>415.403303</v>
       </c>
     </row>
     <row r="160" spans="1:8">
@@ -7264,7 +7264,7 @@
         <v>190.316</v>
       </c>
       <c r="H160">
-        <v>368.30905</v>
+        <v>368.3090482</v>
       </c>
     </row>
     <row r="161" spans="1:8">
@@ -7290,7 +7290,7 @@
         <v>371.48129</v>
       </c>
       <c r="H161">
-        <v>654.94308</v>
+        <v>654.943081</v>
       </c>
     </row>
     <row r="162" spans="1:8">
@@ -7316,7 +7316,7 @@
         <v>202.67246</v>
       </c>
       <c r="H162">
-        <v>336.63127</v>
+        <v>300.0621501</v>
       </c>
     </row>
     <row r="163" spans="1:8">
@@ -7342,7 +7342,7 @@
         <v>209.35737</v>
       </c>
       <c r="H163">
-        <v>415.88804</v>
+        <v>415.8880431</v>
       </c>
     </row>
     <row r="164" spans="1:8">
@@ -7368,7 +7368,7 @@
         <v>325.3154</v>
       </c>
       <c r="H164">
-        <v>938.33806</v>
+        <v>938.3380605</v>
       </c>
     </row>
     <row r="165" spans="1:8">
@@ -7394,7 +7394,7 @@
         <v>336.4296</v>
       </c>
       <c r="H165">
-        <v>803.5694</v>
+        <v>803.5694011000001</v>
       </c>
     </row>
     <row r="166" spans="1:8">
@@ -7420,7 +7420,7 @@
         <v>271.29024</v>
       </c>
       <c r="H166">
-        <v>732.34262</v>
+        <v>732.3426175</v>
       </c>
     </row>
     <row r="167" spans="1:8">
@@ -7446,7 +7446,7 @@
         <v>152.32935</v>
       </c>
       <c r="H167">
-        <v>421.75253</v>
+        <v>421.7525277</v>
       </c>
     </row>
     <row r="168" spans="1:8">
@@ -7472,7 +7472,7 @@
         <v>228.7296</v>
       </c>
       <c r="H168">
-        <v>517.6612699999999</v>
+        <v>517.6612653</v>
       </c>
     </row>
     <row r="169" spans="1:8">
@@ -7498,7 +7498,7 @@
         <v>302.4045</v>
       </c>
       <c r="H169">
-        <v>773.38292</v>
+        <v>773.3829217</v>
       </c>
     </row>
     <row r="170" spans="1:8">
@@ -7524,7 +7524,7 @@
         <v>322.19776</v>
       </c>
       <c r="H170">
-        <v>782.03877</v>
+        <v>782.0387727</v>
       </c>
     </row>
     <row r="171" spans="1:8">
@@ -7550,7 +7550,7 @@
         <v>279.60338</v>
       </c>
       <c r="H171">
-        <v>613.46099</v>
+        <v>613.4609891</v>
       </c>
     </row>
     <row r="172" spans="1:8">
@@ -7576,7 +7576,7 @@
         <v>396.27252</v>
       </c>
       <c r="H172">
-        <v>506.57223</v>
+        <v>506.5722272</v>
       </c>
     </row>
     <row r="173" spans="1:8">
@@ -7602,7 +7602,7 @@
         <v>178.52215</v>
       </c>
       <c r="H173">
-        <v>428.14467</v>
+        <v>428.1446684</v>
       </c>
     </row>
     <row r="174" spans="1:8">
@@ -7628,7 +7628,7 @@
         <v>255.62228</v>
       </c>
       <c r="H174">
-        <v>391.2152</v>
+        <v>391.215196</v>
       </c>
     </row>
     <row r="175" spans="1:8">
@@ -7654,7 +7654,7 @@
         <v>170.19873</v>
       </c>
       <c r="H175">
-        <v>588.09552</v>
+        <v>553.924574</v>
       </c>
     </row>
     <row r="176" spans="1:8">
@@ -7680,7 +7680,7 @@
         <v>105.74777</v>
       </c>
       <c r="H176">
-        <v>297.82799</v>
+        <v>297.8279881</v>
       </c>
     </row>
     <row r="177" spans="1:8">
@@ -7706,7 +7706,7 @@
         <v>211.00058</v>
       </c>
       <c r="H177">
-        <v>367.62184</v>
+        <v>367.6218423</v>
       </c>
     </row>
     <row r="178" spans="1:8">
@@ -7732,7 +7732,7 @@
         <v>97.92359</v>
       </c>
       <c r="H178">
-        <v>250.58448</v>
+        <v>250.5844847</v>
       </c>
     </row>
     <row r="179" spans="1:8">
@@ -7758,7 +7758,7 @@
         <v>88.79913999999999</v>
       </c>
       <c r="H179">
-        <v>239.43117</v>
+        <v>239.4311683</v>
       </c>
     </row>
     <row r="180" spans="1:8">
@@ -7784,7 +7784,7 @@
         <v>225.40718</v>
       </c>
       <c r="H180">
-        <v>374.43406</v>
+        <v>374.4340602</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -7810,7 +7810,7 @@
         <v>150.76349</v>
       </c>
       <c r="H181">
-        <v>445.07167</v>
+        <v>445.0716716</v>
       </c>
     </row>
     <row r="182" spans="1:8">
@@ -7836,7 +7836,7 @@
         <v>107.42387</v>
       </c>
       <c r="H182">
-        <v>278.14489</v>
+        <v>278.1448871</v>
       </c>
     </row>
     <row r="183" spans="1:8">
@@ -7862,7 +7862,7 @@
         <v>180.21112</v>
       </c>
       <c r="H183">
-        <v>431.41469</v>
+        <v>431.4146928</v>
       </c>
     </row>
     <row r="184" spans="1:8">
@@ -7888,7 +7888,7 @@
         <v>191.85406</v>
       </c>
       <c r="H184">
-        <v>448.15893</v>
+        <v>448.158928</v>
       </c>
     </row>
     <row r="185" spans="1:8">
@@ -7914,7 +7914,7 @@
         <v>119.9544</v>
       </c>
       <c r="H185">
-        <v>268.45487</v>
+        <v>268.4548687</v>
       </c>
     </row>
     <row r="186" spans="1:8">
@@ -7940,7 +7940,7 @@
         <v>140.63084</v>
       </c>
       <c r="H186">
-        <v>326.61461</v>
+        <v>326.6146117</v>
       </c>
     </row>
     <row r="187" spans="1:8">
@@ -7966,7 +7966,7 @@
         <v>205.99145</v>
       </c>
       <c r="H187">
-        <v>364.70339</v>
+        <v>364.7033895</v>
       </c>
     </row>
     <row r="188" spans="1:8">
@@ -7992,7 +7992,7 @@
         <v>277.18774</v>
       </c>
       <c r="H188">
-        <v>401.369</v>
+        <v>401.369003</v>
       </c>
     </row>
     <row r="189" spans="1:8">
@@ -8018,7 +8018,7 @@
         <v>151.8269</v>
       </c>
       <c r="H189">
-        <v>412.85645</v>
+        <v>412.8564547</v>
       </c>
     </row>
     <row r="190" spans="1:8">
@@ -8044,7 +8044,7 @@
         <v>149.85528</v>
       </c>
       <c r="H190">
-        <v>388.26723</v>
+        <v>388.2672312</v>
       </c>
     </row>
     <row r="191" spans="1:8">
@@ -8070,7 +8070,7 @@
         <v>140.24703</v>
       </c>
       <c r="H191">
-        <v>335.81061</v>
+        <v>335.8106144</v>
       </c>
     </row>
     <row r="192" spans="1:8">
@@ -8096,7 +8096,7 @@
         <v>150.42216</v>
       </c>
       <c r="H192">
-        <v>351.52705</v>
+        <v>351.5270481</v>
       </c>
     </row>
     <row r="193" spans="1:8">
@@ -8122,7 +8122,7 @@
         <v>17.92449</v>
       </c>
       <c r="H193">
-        <v>102.56975</v>
+        <v>102.5697527</v>
       </c>
     </row>
     <row r="194" spans="1:8">
@@ -8148,7 +8148,7 @@
         <v>26.74722</v>
       </c>
       <c r="H194">
-        <v>122.72399</v>
+        <v>122.7239905</v>
       </c>
     </row>
     <row r="195" spans="1:8">
@@ -8174,7 +8174,7 @@
         <v>220.47432</v>
       </c>
       <c r="H195">
-        <v>372.75579</v>
+        <v>372.7557887</v>
       </c>
     </row>
     <row r="196" spans="1:8">
@@ -8200,7 +8200,7 @@
         <v>210.56813</v>
       </c>
       <c r="H196">
-        <v>362.36918</v>
+        <v>362.3691825</v>
       </c>
     </row>
     <row r="197" spans="1:8">
@@ -8226,7 +8226,7 @@
         <v>236.31905</v>
       </c>
       <c r="H197">
-        <v>562.83889</v>
+        <v>562.838889</v>
       </c>
     </row>
     <row r="198" spans="1:8">
@@ -8252,7 +8252,7 @@
         <v>330.62856</v>
       </c>
       <c r="H198">
-        <v>686.18782</v>
+        <v>686.1878220999999</v>
       </c>
     </row>
     <row r="199" spans="1:8">
@@ -8278,7 +8278,7 @@
         <v>197.37652</v>
       </c>
       <c r="H199">
-        <v>642.90643</v>
+        <v>642.9064319</v>
       </c>
     </row>
     <row r="200" spans="1:8">
@@ -8304,7 +8304,7 @@
         <v>192.48525</v>
       </c>
       <c r="H200">
-        <v>513.01105</v>
+        <v>513.011045</v>
       </c>
     </row>
     <row r="201" spans="1:8">
@@ -8330,7 +8330,7 @@
         <v>233.43889</v>
       </c>
       <c r="H201">
-        <v>441.11442</v>
+        <v>441.1144183</v>
       </c>
     </row>
     <row r="202" spans="1:8">
@@ -8356,7 +8356,7 @@
         <v>348.98068</v>
       </c>
       <c r="H202">
-        <v>551.33848</v>
+        <v>551.3384769</v>
       </c>
     </row>
     <row r="203" spans="1:8">
@@ -8382,7 +8382,7 @@
         <v>252.8204</v>
       </c>
       <c r="H203">
-        <v>672.2715899999999</v>
+        <v>672.2715877000001</v>
       </c>
     </row>
     <row r="204" spans="1:8">
@@ -8408,7 +8408,7 @@
         <v>151.33173</v>
       </c>
       <c r="H204">
-        <v>440.60215</v>
+        <v>440.6021479</v>
       </c>
     </row>
     <row r="205" spans="1:8">
@@ -8434,7 +8434,7 @@
         <v>149.44977</v>
       </c>
       <c r="H205">
-        <v>382.60085</v>
+        <v>382.6008489</v>
       </c>
     </row>
     <row r="206" spans="1:8">
@@ -8460,7 +8460,7 @@
         <v>210.73209</v>
       </c>
       <c r="H206">
-        <v>399.47935</v>
+        <v>399.4793515</v>
       </c>
     </row>
     <row r="207" spans="1:8">
@@ -8486,7 +8486,7 @@
         <v>497.43294</v>
       </c>
       <c r="H207">
-        <v>1658.32055</v>
+        <v>1658.320548</v>
       </c>
     </row>
     <row r="208" spans="1:8">
@@ -8512,7 +8512,7 @@
         <v>199.60434</v>
       </c>
       <c r="H208">
-        <v>326.98037</v>
+        <v>326.980373</v>
       </c>
     </row>
     <row r="209" spans="1:8">
@@ -8538,7 +8538,7 @@
         <v>172.71988</v>
       </c>
       <c r="H209">
-        <v>320.0076</v>
+        <v>320.0075982</v>
       </c>
     </row>
     <row r="210" spans="1:8">
@@ -8564,7 +8564,7 @@
         <v>85.17728</v>
       </c>
       <c r="H210">
-        <v>201.77808</v>
+        <v>201.7780775</v>
       </c>
     </row>
     <row r="211" spans="1:8">
@@ -8590,7 +8590,7 @@
         <v>384.43191</v>
       </c>
       <c r="H211">
-        <v>689.01881</v>
+        <v>689.0188056</v>
       </c>
     </row>
     <row r="212" spans="1:8">
@@ -8616,7 +8616,7 @@
         <v>426.67282</v>
       </c>
       <c r="H212">
-        <v>530.80223</v>
+        <v>472.0755625</v>
       </c>
     </row>
     <row r="213" spans="1:8">
@@ -8642,7 +8642,7 @@
         <v>447.55909</v>
       </c>
       <c r="H213">
-        <v>520.14555</v>
+        <v>520.1455457</v>
       </c>
     </row>
     <row r="214" spans="1:8">
@@ -8668,7 +8668,7 @@
         <v>420.91045</v>
       </c>
       <c r="H214">
-        <v>903.16304</v>
+        <v>903.1630376000001</v>
       </c>
     </row>
     <row r="215" spans="1:8">
@@ -8694,7 +8694,7 @@
         <v>206.02593</v>
       </c>
       <c r="H215">
-        <v>604.8734899999999</v>
+        <v>604.8734873</v>
       </c>
     </row>
     <row r="216" spans="1:8">
